--- a/output/roomself_excel/9238.xlsx
+++ b/output/roomself_excel/9238.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>108298</v>
+        <v>117528</v>
       </c>
       <c r="D2" t="n">
-        <v>2636</v>
+        <v>2744</v>
       </c>
       <c r="E2" t="n">
-        <v>346</v>
+        <v>391</v>
       </c>
       <c r="F2" t="n">
-        <v>25</v>
+        <v>371</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>109550</v>
+        <v>113520</v>
       </c>
       <c r="D3" t="n">
-        <v>2652</v>
+        <v>2696</v>
       </c>
       <c r="E3" t="n">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="F3" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>412303</v>
+        <v>228915</v>
       </c>
       <c r="D4" t="n">
-        <v>6604</v>
+        <v>3852</v>
       </c>
       <c r="E4" t="n">
-        <v>899</v>
+        <v>528</v>
       </c>
       <c r="F4" t="n">
-        <v>391</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5">
@@ -532,17 +532,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>87033</v>
+        <v>224400</v>
       </c>
       <c r="D5" t="n">
-        <v>2536</v>
+        <v>3812</v>
       </c>
       <c r="E5" t="n">
-        <v>201</v>
+        <v>528</v>
       </c>
       <c r="F5" t="n">
         <v>37</v>
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>83725</v>
+        <v>96051</v>
       </c>
       <c r="D6" t="n">
-        <v>2488</v>
+        <v>2480</v>
       </c>
       <c r="E6" t="n">
-        <v>462</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>234</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>402885</v>
+        <v>96960</v>
       </c>
       <c r="D7" t="n">
-        <v>6552</v>
+        <v>2492</v>
       </c>
       <c r="E7" t="n">
-        <v>858</v>
+        <v>303</v>
       </c>
       <c r="F7" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>494494</v>
+        <v>125828</v>
       </c>
       <c r="D8" t="n">
-        <v>5631</v>
+        <v>2844</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>332</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
@@ -624,16 +624,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>96051</v>
+        <v>123704</v>
       </c>
       <c r="D9" t="n">
-        <v>2480</v>
+        <v>2820</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>329</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>96960</v>
+        <v>97002</v>
       </c>
       <c r="D10" t="n">
         <v>2492</v>
       </c>
       <c r="E10" t="n">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="F10" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>61070</v>
+        <v>96960</v>
       </c>
       <c r="D11" t="n">
-        <v>2028</v>
+        <v>2492</v>
       </c>
       <c r="E11" t="n">
-        <v>586</v>
+        <v>359</v>
       </c>
       <c r="F11" t="n">
-        <v>234</v>
+        <v>342</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>20562</v>
+        <v>61070</v>
       </c>
       <c r="D12" t="n">
-        <v>1148</v>
+        <v>2028</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">
@@ -752,14 +752,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20536</v>
+        <v>61506</v>
       </c>
       <c r="D15" t="n">
-        <v>1148</v>
+        <v>2028</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -774,20 +774,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>61506</v>
+        <v>64965</v>
       </c>
       <c r="D16" t="n">
-        <v>2028</v>
+        <v>2152</v>
       </c>
       <c r="E16" t="n">
-        <v>273</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>201</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -796,20 +796,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>125828</v>
+        <v>65860</v>
       </c>
       <c r="D17" t="n">
-        <v>2844</v>
+        <v>2164</v>
       </c>
       <c r="E17" t="n">
-        <v>332</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -818,20 +818,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>123704</v>
+        <v>34038</v>
       </c>
       <c r="D18" t="n">
-        <v>2820</v>
+        <v>1476</v>
       </c>
       <c r="E18" t="n">
-        <v>329</v>
+        <v>183</v>
       </c>
       <c r="F18" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19">
@@ -840,20 +840,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>97002</v>
+        <v>33670</v>
       </c>
       <c r="D19" t="n">
-        <v>2492</v>
+        <v>1468</v>
       </c>
       <c r="E19" t="n">
-        <v>317</v>
+        <v>185</v>
       </c>
       <c r="F19" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -862,20 +862,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>96960</v>
+        <v>108298</v>
       </c>
       <c r="D20" t="n">
-        <v>2492</v>
+        <v>2636</v>
       </c>
       <c r="E20" t="n">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="F20" t="n">
-        <v>342</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
@@ -884,20 +884,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>40874</v>
+        <v>109550</v>
       </c>
       <c r="D21" t="n">
-        <v>1620</v>
+        <v>2652</v>
       </c>
       <c r="E21" t="n">
-        <v>191</v>
+        <v>350</v>
       </c>
       <c r="F21" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22">
@@ -906,20 +906,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>41040</v>
+        <v>20562</v>
       </c>
       <c r="D22" t="n">
-        <v>1624</v>
+        <v>1148</v>
       </c>
       <c r="E22" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -928,20 +928,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>34038</v>
+        <v>20536</v>
       </c>
       <c r="D23" t="n">
-        <v>1476</v>
+        <v>1148</v>
       </c>
       <c r="E23" t="n">
-        <v>183</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -950,19 +950,107 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>33670</v>
+        <v>494494</v>
       </c>
       <c r="D24" t="n">
-        <v>1468</v>
+        <v>5631</v>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>87033</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2536</v>
+      </c>
+      <c r="E25" t="n">
+        <v>201</v>
+      </c>
+      <c r="F25" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>83725</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2488</v>
+      </c>
+      <c r="E26" t="n">
+        <v>462</v>
+      </c>
+      <c r="F26" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>40874</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1620</v>
+      </c>
+      <c r="E27" t="n">
+        <v>191</v>
+      </c>
+      <c r="F27" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>41040</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1624</v>
+      </c>
+      <c r="E28" t="n">
+        <v>190</v>
+      </c>
+      <c r="F28" t="n">
         <v>39</v>
       </c>
     </row>

--- a/output/roomself_excel/9238.xlsx
+++ b/output/roomself_excel/9238.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>2744</v>
       </c>
-      <c r="E2" t="n">
-        <v>391</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>371</v>
+        <v>332</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>354</v>
+      </c>
+      <c r="J2" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="3">
@@ -497,11 +533,27 @@
       <c r="D3" t="n">
         <v>2696</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>330</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>37</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>344</v>
+      </c>
+      <c r="J3" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="4">
@@ -519,12 +571,20 @@
       <c r="D4" t="n">
         <v>3852</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>528</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>37</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +601,20 @@
       <c r="D5" t="n">
         <v>3812</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>528</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>37</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +631,20 @@
       <c r="D6" t="n">
         <v>2480</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="G6" t="n">
+        <v>36</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +661,20 @@
       <c r="D7" t="n">
         <v>2492</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>303</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>39</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +691,20 @@
       <c r="D8" t="n">
         <v>2844</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>332</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>45</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +721,20 @@
       <c r="D9" t="n">
         <v>2820</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>329</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>39</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,10 +751,26 @@
       <c r="D10" t="n">
         <v>2492</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>306</v>
+      </c>
+      <c r="G10" t="n">
+        <v>36</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>317</v>
       </c>
-      <c r="F10" t="n">
+      <c r="J10" t="n">
         <v>45</v>
       </c>
     </row>
@@ -673,11 +789,27 @@
       <c r="D11" t="n">
         <v>2492</v>
       </c>
-      <c r="E11" t="n">
-        <v>359</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>342</v>
+        <v>303</v>
+      </c>
+      <c r="G11" t="n">
+        <v>39</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>320</v>
+      </c>
+      <c r="J11" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="12">
@@ -695,12 +827,20 @@
       <c r="D12" t="n">
         <v>2028</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>239</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>37</v>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +857,12 @@
       <c r="D13" t="n">
         <v>1320</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +879,12 @@
       <c r="D14" t="n">
         <v>1324</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +901,12 @@
       <c r="D15" t="n">
         <v>2028</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +923,12 @@
       <c r="D16" t="n">
         <v>2152</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +945,12 @@
       <c r="D17" t="n">
         <v>2164</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +967,20 @@
       <c r="D18" t="n">
         <v>1476</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>183</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>45</v>
       </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +997,20 @@
       <c r="D19" t="n">
         <v>1468</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
         <v>185</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>39</v>
       </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1027,20 @@
       <c r="D20" t="n">
         <v>2636</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
         <v>346</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>25</v>
       </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1057,20 @@
       <c r="D21" t="n">
         <v>2652</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
         <v>350</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>25</v>
       </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,12 +1087,12 @@
       <c r="D22" t="n">
         <v>1148</v>
       </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -937,12 +1109,12 @@
       <c r="D23" t="n">
         <v>1148</v>
       </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,12 +1131,12 @@
       <c r="D24" t="n">
         <v>5631</v>
       </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -981,12 +1153,20 @@
       <c r="D25" t="n">
         <v>2536</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
         <v>201</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>37</v>
       </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1003,11 +1183,27 @@
       <c r="D26" t="n">
         <v>2488</v>
       </c>
-      <c r="E26" t="n">
-        <v>462</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F26" t="n">
-        <v>234</v>
+        <v>197</v>
+      </c>
+      <c r="G26" t="n">
+        <v>37</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>95</v>
+      </c>
+      <c r="J26" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="27">
@@ -1025,12 +1221,20 @@
       <c r="D27" t="n">
         <v>1620</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
         <v>191</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>45</v>
       </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1047,12 +1251,20 @@
       <c r="D28" t="n">
         <v>1624</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
         <v>190</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>39</v>
       </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/9238.xlsx
+++ b/output/roomself_excel/9238.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,26 @@
           <t>ExtWallWidth_2</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -517,6 +537,22 @@
       <c r="J2" t="n">
         <v>39</v>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>131</v>
+      </c>
+      <c r="N2" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -555,6 +591,22 @@
       <c r="J3" t="n">
         <v>36</v>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>132</v>
+      </c>
+      <c r="N3" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -585,6 +637,22 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>269</v>
+      </c>
+      <c r="N4" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -615,6 +683,22 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>272</v>
+      </c>
+      <c r="N5" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -645,6 +729,22 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>156</v>
+      </c>
+      <c r="N6" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -675,6 +775,22 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>148</v>
+      </c>
+      <c r="N7" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -705,6 +821,22 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>156</v>
+      </c>
+      <c r="N8" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -735,6 +867,22 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>149</v>
+      </c>
+      <c r="N9" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -773,6 +921,22 @@
       <c r="J10" t="n">
         <v>45</v>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>153</v>
+      </c>
+      <c r="N10" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -811,6 +975,22 @@
       <c r="J11" t="n">
         <v>39</v>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>152</v>
+      </c>
+      <c r="N11" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -841,6 +1021,10 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -863,6 +1047,10 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -885,6 +1073,10 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -907,6 +1099,10 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -929,6 +1125,10 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -951,6 +1151,10 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -981,6 +1185,22 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>96</v>
+      </c>
+      <c r="N18" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1011,6 +1231,22 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>94</v>
+      </c>
+      <c r="N19" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1041,6 +1277,22 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>101</v>
+      </c>
+      <c r="N20" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1071,6 +1323,22 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>100</v>
+      </c>
+      <c r="N21" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1093,6 +1361,10 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1115,6 +1387,10 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1137,6 +1413,10 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1167,6 +1447,22 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>88</v>
+      </c>
+      <c r="N25" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1205,6 +1501,22 @@
       <c r="J26" t="n">
         <v>37</v>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>84</v>
+      </c>
+      <c r="N26" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1235,6 +1547,22 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>101</v>
+      </c>
+      <c r="N27" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1265,6 +1593,22 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>98</v>
+      </c>
+      <c r="N28" t="n">
+        <v>39</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
